--- a/data/b2_indio/B2 Índio 02-2026.xlsx
+++ b/data/b2_indio/B2 Índio 02-2026.xlsx
@@ -4420,25 +4420,25 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>327.7</v>
+        <v>343.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1228.17</v>
+        <v>52833.6</v>
       </c>
     </row>
     <row r="4">
@@ -4447,214 +4447,214 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>51299.45</v>
+        <v>2278.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46059</v>
+        <v>46061</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1657.47</v>
+        <v>3026.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46061</v>
+        <v>46063</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>2979.63</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2559.13</v>
+        <v>1547.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2435.68</v>
+        <v>1869.18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46063</v>
+        <v>46068</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>3900</v>
+        <v>10131.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1508.8</v>
+        <v>1556.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46065</v>
+        <v>46068</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>2161.53</v>
+        <v>3002.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46068</v>
+        <v>46072</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>10315.6</v>
+        <v>2745.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46068</v>
+        <v>46073</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1319.67</v>
+        <v>18121.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46068</v>
+        <v>46074</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2926.52</v>
+        <v>1344.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46073</v>
+        <v>46075</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>18432.15</v>
+        <v>1055.03</v>
       </c>
     </row>
     <row r="16">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3193.24</v>
+        <v>3111.96</v>
       </c>
     </row>
     <row r="17">
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2632.66</v>
+        <v>2839.72</v>
       </c>
     </row>
   </sheetData>
